--- a/tabtools/qa/output/tablex_numfmt_t1.xlsx
+++ b/tabtools/qa/output/tablex_numfmt_t1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="18">
   <si>
     <t>Table</t>
   </si>
@@ -73,10 +73,492 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="114">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="227">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -569,7 +1051,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="80">
+  <borders count="159">
     <border>
       <left/>
       <right/>
@@ -1106,11 +1588,540 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -1413,6 +2424,310 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="113" fillId="0" borderId="79" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0"/>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="84" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="85" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="86" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="87" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="88" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="143" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="145" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="147" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="156" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="158" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="160" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="162" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="164" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="166" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="176" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="178" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="180" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="181" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="182" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="183" fillId="0" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="184" fillId="0" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="185" fillId="0" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="186" fillId="0" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="187" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="210" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="212" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="214" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="216" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="218" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="220" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="222" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="224" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="226" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1428,110 +2743,110 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="3" customWidth="true"/>
-    <col min="3" max="5" width="15.7109375" style="4" customWidth="true"/>
+    <col min="1" max="1" width="2.7109375" style="81" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="82" customWidth="true"/>
+    <col min="3" max="5" width="15.7109375" style="83" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="25" t="s">
+    <row r="1" s="80" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="104" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="D1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="104" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="127" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="138" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="134" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="52" t="s">
+      <c r="D3" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="60" t="s">
+      <c r="E3" s="139" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="147" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="69">
+      <c r="C4" s="148">
         <v>6072.4230769230771</v>
       </c>
-      <c r="D4" s="70">
+      <c r="D4" s="149">
         <v>19.82692307692308</v>
       </c>
-      <c r="E4" s="71">
+      <c r="E4" s="150">
         <v>3317.1153846153852</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="73">
+      <c r="C5" s="152">
         <v>6384.681818181818</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D5" s="153">
         <v>24.77272727272727</v>
       </c>
-      <c r="E5" s="75">
+      <c r="E5" s="154">
         <v>2315.909090909091</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="155" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="77">
+      <c r="C6" s="156">
         <v>6165.2567567567567</v>
       </c>
-      <c r="D6" s="78">
+      <c r="D6" s="157">
         <v>21.297297297297298</v>
       </c>
-      <c r="E6" s="79">
+      <c r="E6" s="158">
         <v>3019.45945945946</v>
       </c>
     </row>
